--- a/9. SW Writing 이력 관리/HKMC_SW_Writing_이력_관리_250721.xlsx
+++ b/9. SW Writing 이력 관리/HKMC_SW_Writing_이력_관리_250721.xlsx
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="63">
   <si>
     <t>일  자</t>
   </si>
@@ -369,12 +369,53 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AY Heater Control Zig Writing 이력 기입</t>
+    <t>김진겸</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIR PTC HTR팀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김진겸</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>BJ1 250529_comptemp_snr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250717 QV sync 프로그램</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIR PTC HTR팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서동권 사원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V01.13.01A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력제어성 검증용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rear시료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AY Heater Control Zig Writing 이력 기입
+BJ1, MVa Rear 이력 기입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -985,12 +1026,12 @@
         <v>50</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
@@ -1138,37 +1179,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:H17"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="B18:D18"/>
@@ -1177,6 +1187,37 @@
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:H20"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.15748031496062992" top="0.78740157480314965" bottom="0.72" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -1724,14 +1765,30 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="C4" s="11">
+        <v>45859</v>
+      </c>
+      <c r="D4" s="11">
+        <v>45859</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
@@ -3936,14 +3993,30 @@
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+      <c r="C3" s="11">
+        <v>45859</v>
+      </c>
+      <c r="D3" s="11">
+        <v>45859</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="7">

--- a/9. SW Writing 이력 관리/HKMC_SW_Writing_이력_관리_250721.xlsx
+++ b/9. SW Writing 이력 관리/HKMC_SW_Writing_이력_관리_250721.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\PROJECT\Gitlab\HMC\ptc_heater_doc\9. SW Writing 이력 관리\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\일정\ptc_heater_doc\9. SW Writing 이력 관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11760" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="이력관리" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="80">
   <si>
     <t>일  자</t>
   </si>
@@ -415,6 +415,74 @@
   <si>
     <t>AY Heater Control Zig Writing 이력 기입
 BJ1, MVa Rear 이력 기입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QV 01.03.01 Unused</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QV 01.03.01 Unused</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌우전력 3.65% 미적용 SW Writing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌우전력 3.65% 미적용, Limit 3600W SW Writing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIR PTC HTR팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장종현 사원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVm 01.02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬로박 EOL 마스터 샘플</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한온 테스트 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌우전력 3.65%, Limit 3600W, 소프트 스타트 적용 SW Writing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장종현 사원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V01.00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01.01.03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1EA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고품 분석</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1179,6 +1247,37 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:H17"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="B18:D18"/>
@@ -1187,37 +1286,6 @@
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:H20"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.15748031496062992" top="0.78740157480314965" bottom="0.72" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -1236,7 +1304,7 @@
   <cols>
     <col min="3" max="4" width="17.125" style="10" customWidth="1"/>
     <col min="5" max="9" width="23.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="32.25" style="10" customWidth="1"/>
+    <col min="10" max="10" width="58.375" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
@@ -1307,27 +1375,59 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="C4" s="11">
+        <v>45951</v>
+      </c>
+      <c r="D4" s="11">
+        <v>45951</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="C5" s="11">
+        <v>45951</v>
+      </c>
+      <c r="D5" s="11">
+        <v>45951</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
@@ -1694,7 +1794,7 @@
   <cols>
     <col min="3" max="4" width="17.125" style="10" customWidth="1"/>
     <col min="5" max="9" width="23.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="32.25" style="10" customWidth="1"/>
+    <col min="10" max="10" width="46.125" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
@@ -1794,40 +1894,86 @@
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="C5" s="11">
+        <v>45966</v>
+      </c>
+      <c r="D5" s="11">
+        <v>45966</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="C6" s="11">
+        <v>45966</v>
+      </c>
+      <c r="D6" s="11">
+        <v>45966</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="C7" s="11">
+        <v>45966</v>
+      </c>
+      <c r="D7" s="11">
+        <v>45966</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
@@ -2688,13 +2834,27 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="C4" s="11">
+        <v>45945</v>
+      </c>
+      <c r="D4" s="11">
+        <v>45945</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -5753,13 +5913,27 @@
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
+      <c r="C3" s="11">
+        <v>45944</v>
+      </c>
+      <c r="D3" s="11">
+        <v>45944</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
